--- a/activitereeldirect-2026.xlsx
+++ b/activitereeldirect-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE24AF0F-0E11-4056-AC56-4D65E90EB418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38BB671-B2A7-4E4F-BB6F-FDCA87389928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52F3EE67-8AA3-4B10-A5A9-DE88DE815FD5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="107">
   <si>
     <t>N°commande</t>
   </si>
@@ -345,6 +345,18 @@
   </si>
   <si>
     <t>Mars</t>
+  </si>
+  <si>
+    <t>26404913</t>
+  </si>
+  <si>
+    <t>26605307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE KEVIN                </t>
+  </si>
+  <si>
+    <t>Février</t>
   </si>
 </sst>
 </file>
@@ -720,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA07812-0C85-468D-8FD3-167ED09F5A69}">
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -1788,6 +1800,219 @@
         <v>102</v>
       </c>
     </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46071</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>85.68</v>
+      </c>
+      <c r="L16">
+        <v>85.68</v>
+      </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="1">
+        <v>46071</v>
+      </c>
+      <c r="P16" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T16" t="s">
+        <v>61</v>
+      </c>
+      <c r="U16" t="s">
+        <v>62</v>
+      </c>
+      <c r="V16" t="s">
+        <v>63</v>
+      </c>
+      <c r="W16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46071</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>247.96</v>
+      </c>
+      <c r="L17">
+        <v>247.96</v>
+      </c>
+      <c r="M17" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="1">
+        <v>46071</v>
+      </c>
+      <c r="P17" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" t="s">
+        <v>34</v>
+      </c>
+      <c r="T17" t="s">
+        <v>61</v>
+      </c>
+      <c r="U17" t="s">
+        <v>62</v>
+      </c>
+      <c r="V17" t="s">
+        <v>63</v>
+      </c>
+      <c r="W17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46071</v>
+      </c>
+      <c r="G18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>25.44</v>
+      </c>
+      <c r="L18">
+        <v>76.319999999999993</v>
+      </c>
+      <c r="M18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="1">
+        <v>46071</v>
+      </c>
+      <c r="P18" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" t="s">
+        <v>62</v>
+      </c>
+      <c r="V18" t="s">
+        <v>63</v>
+      </c>
+      <c r="W18" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/activitereeldirect-2026.xlsx
+++ b/activitereeldirect-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38BB671-B2A7-4E4F-BB6F-FDCA87389928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7808DC2A-957B-4F25-B1F6-FD755CACF936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52F3EE67-8AA3-4B10-A5A9-DE88DE815FD5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="137">
   <si>
     <t>N°commande</t>
   </si>
@@ -357,6 +357,96 @@
   </si>
   <si>
     <t>Février</t>
+  </si>
+  <si>
+    <t>26410130</t>
+  </si>
+  <si>
+    <t>26610835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MME THOMAS           </t>
+  </si>
+  <si>
+    <t>TEAM CAPIN SEBASTIEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86668 10                 </t>
+  </si>
+  <si>
+    <t>86668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTI-BOND HT AER.500ML COLLE CONTACT                        </t>
+  </si>
+  <si>
+    <t>26411504</t>
+  </si>
+  <si>
+    <t>26612459</t>
+  </si>
+  <si>
+    <t>26338456</t>
+  </si>
+  <si>
+    <t>556934</t>
+  </si>
+  <si>
+    <t>SCANIA NORMANDIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I71_26040695_MAA         </t>
+  </si>
+  <si>
+    <t>ROND POINT DE LA RUE FRANCOIS ARAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88091 22                 </t>
+  </si>
+  <si>
+    <t>88091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCREENFIX 90 SAUCISSE CARTOUCHE 400ML                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1467 33                 </t>
+  </si>
+  <si>
+    <t>A1467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS SPONGE FINE 30/PK                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1468 33                 </t>
+  </si>
+  <si>
+    <t>A1468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS SPONGE SUPER FINE 30/PK                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0107 00                 </t>
+  </si>
+  <si>
+    <t>E0107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDE TRESSEE 22 M TW-72                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0209 00                 </t>
+  </si>
+  <si>
+    <t>E0209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDE A PIANO CARREE 22M                                     </t>
+  </si>
+  <si>
+    <t>Avril</t>
   </si>
 </sst>
 </file>
@@ -732,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA07812-0C85-468D-8FD3-167ED09F5A69}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -2013,6 +2103,574 @@
         <v>106</v>
       </c>
     </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+      <c r="K19">
+        <v>38.75</v>
+      </c>
+      <c r="L19">
+        <v>232.5</v>
+      </c>
+      <c r="M19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" s="1">
+        <v>46125</v>
+      </c>
+      <c r="P19" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="s">
+        <v>33</v>
+      </c>
+      <c r="S19" t="s">
+        <v>110</v>
+      </c>
+      <c r="T19" t="s">
+        <v>48</v>
+      </c>
+      <c r="U19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20">
+        <v>6</v>
+      </c>
+      <c r="K20">
+        <v>23.63</v>
+      </c>
+      <c r="L20">
+        <v>141.78</v>
+      </c>
+      <c r="M20" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="1">
+        <v>46125</v>
+      </c>
+      <c r="P20" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" t="s">
+        <v>33</v>
+      </c>
+      <c r="S20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T20" t="s">
+        <v>48</v>
+      </c>
+      <c r="U20" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" t="s">
+        <v>50</v>
+      </c>
+      <c r="W20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>-204.29</v>
+      </c>
+      <c r="L21">
+        <v>-204.29</v>
+      </c>
+      <c r="M21" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" t="s">
+        <v>110</v>
+      </c>
+      <c r="T21" t="s">
+        <v>48</v>
+      </c>
+      <c r="U21" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" t="s">
+        <v>120</v>
+      </c>
+      <c r="W21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22">
+        <v>24</v>
+      </c>
+      <c r="K22">
+        <v>31.11</v>
+      </c>
+      <c r="L22">
+        <v>746.64</v>
+      </c>
+      <c r="M22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P22" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" t="s">
+        <v>110</v>
+      </c>
+      <c r="T22" t="s">
+        <v>48</v>
+      </c>
+      <c r="U22" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" t="s">
+        <v>120</v>
+      </c>
+      <c r="W22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>28.57</v>
+      </c>
+      <c r="L23">
+        <v>57.14</v>
+      </c>
+      <c r="M23" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P23" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" t="s">
+        <v>110</v>
+      </c>
+      <c r="T23" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" t="s">
+        <v>120</v>
+      </c>
+      <c r="W23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>28.57</v>
+      </c>
+      <c r="L24">
+        <v>57.14</v>
+      </c>
+      <c r="M24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P24" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" t="s">
+        <v>110</v>
+      </c>
+      <c r="T24" t="s">
+        <v>48</v>
+      </c>
+      <c r="U24" t="s">
+        <v>49</v>
+      </c>
+      <c r="V24" t="s">
+        <v>120</v>
+      </c>
+      <c r="W24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G25" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" t="s">
+        <v>132</v>
+      </c>
+      <c r="J25">
+        <v>5</v>
+      </c>
+      <c r="K25">
+        <v>53.25</v>
+      </c>
+      <c r="L25">
+        <v>266.25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P25" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" t="s">
+        <v>110</v>
+      </c>
+      <c r="T25" t="s">
+        <v>48</v>
+      </c>
+      <c r="U25" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" t="s">
+        <v>120</v>
+      </c>
+      <c r="W25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" t="s">
+        <v>134</v>
+      </c>
+      <c r="I26" t="s">
+        <v>135</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+      <c r="K26">
+        <v>46.95</v>
+      </c>
+      <c r="L26">
+        <v>234.75</v>
+      </c>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P26" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" t="s">
+        <v>110</v>
+      </c>
+      <c r="T26" t="s">
+        <v>48</v>
+      </c>
+      <c r="U26" t="s">
+        <v>49</v>
+      </c>
+      <c r="V26" t="s">
+        <v>120</v>
+      </c>
+      <c r="W26" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/activitereeldirect-2026.xlsx
+++ b/activitereeldirect-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7808DC2A-957B-4F25-B1F6-FD755CACF936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ED8657-D29D-4878-8F4B-FEBC2D942FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52F3EE67-8AA3-4B10-A5A9-DE88DE815FD5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="168">
   <si>
     <t>N°commande</t>
   </si>
@@ -447,6 +447,99 @@
   </si>
   <si>
     <t>Avril</t>
+  </si>
+  <si>
+    <t>26412614</t>
+  </si>
+  <si>
+    <t>26613482</t>
+  </si>
+  <si>
+    <t>26179181</t>
+  </si>
+  <si>
+    <t>MULTI CHOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE FREDERIC MAGASIN     </t>
+  </si>
+  <si>
+    <t>BEUZEVILLE</t>
+  </si>
+  <si>
+    <t>27210</t>
+  </si>
+  <si>
+    <t>ROUTE D EPAIGNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83970 24                 </t>
+  </si>
+  <si>
+    <t>83970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDD NETTOYANT INJECTION 250 ML                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86547 10                 </t>
+  </si>
+  <si>
+    <t>86547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPF FOAM CLEANER 500ML                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87086 22                 </t>
+  </si>
+  <si>
+    <t>87086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UREA ANTI CRYSTAL ADDITIVE BOUT 250 ML                       </t>
+  </si>
+  <si>
+    <t>26413451</t>
+  </si>
+  <si>
+    <t>26614390</t>
+  </si>
+  <si>
+    <t>565075</t>
+  </si>
+  <si>
+    <t>26309070</t>
+  </si>
+  <si>
+    <t>ELBA MOULT</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4501379385               </t>
+  </si>
+  <si>
+    <t>MOULT</t>
+  </si>
+  <si>
+    <t>14370</t>
+  </si>
+  <si>
+    <t>19 RUE REMBRANDT BUGATTI ZI</t>
+  </si>
+  <si>
+    <t>26413452</t>
+  </si>
+  <si>
+    <t>26614391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE TEL KARL             </t>
+  </si>
+  <si>
+    <t>Mai</t>
   </si>
 </sst>
 </file>
@@ -456,10 +549,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -822,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA07812-0C85-468D-8FD3-167ED09F5A69}">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -2671,7 +2770,647 @@
         <v>136</v>
       </c>
     </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>-109.53</v>
+      </c>
+      <c r="L27">
+        <v>-109.53</v>
+      </c>
+      <c r="M27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P27" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="s">
+        <v>33</v>
+      </c>
+      <c r="S27" t="s">
+        <v>110</v>
+      </c>
+      <c r="T27" t="s">
+        <v>142</v>
+      </c>
+      <c r="U27" t="s">
+        <v>143</v>
+      </c>
+      <c r="V27" t="s">
+        <v>144</v>
+      </c>
+      <c r="W27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H28" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+      <c r="J28">
+        <v>12</v>
+      </c>
+      <c r="K28">
+        <v>18.52</v>
+      </c>
+      <c r="L28">
+        <v>222.24</v>
+      </c>
+      <c r="M28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P28" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="s">
+        <v>33</v>
+      </c>
+      <c r="S28" t="s">
+        <v>110</v>
+      </c>
+      <c r="T28" t="s">
+        <v>142</v>
+      </c>
+      <c r="U28" t="s">
+        <v>143</v>
+      </c>
+      <c r="V28" t="s">
+        <v>144</v>
+      </c>
+      <c r="W28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G29" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I29" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29">
+        <v>12</v>
+      </c>
+      <c r="K29">
+        <v>19.52</v>
+      </c>
+      <c r="L29">
+        <v>234.24</v>
+      </c>
+      <c r="M29" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P29" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" t="s">
+        <v>110</v>
+      </c>
+      <c r="T29" t="s">
+        <v>142</v>
+      </c>
+      <c r="U29" t="s">
+        <v>143</v>
+      </c>
+      <c r="V29" t="s">
+        <v>144</v>
+      </c>
+      <c r="W29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s">
+        <v>75</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>34.11</v>
+      </c>
+      <c r="L30">
+        <v>34.11</v>
+      </c>
+      <c r="M30" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P30" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30" t="s">
+        <v>110</v>
+      </c>
+      <c r="T30" t="s">
+        <v>142</v>
+      </c>
+      <c r="U30" t="s">
+        <v>143</v>
+      </c>
+      <c r="V30" t="s">
+        <v>144</v>
+      </c>
+      <c r="W30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G31" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>153</v>
+      </c>
+      <c r="J31">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <v>15.53</v>
+      </c>
+      <c r="L31">
+        <v>186.36</v>
+      </c>
+      <c r="M31" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P31" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" t="s">
+        <v>110</v>
+      </c>
+      <c r="T31" t="s">
+        <v>142</v>
+      </c>
+      <c r="U31" t="s">
+        <v>143</v>
+      </c>
+      <c r="V31" t="s">
+        <v>144</v>
+      </c>
+      <c r="W31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G32" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" t="s">
+        <v>131</v>
+      </c>
+      <c r="I32" t="s">
+        <v>132</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>53.25</v>
+      </c>
+      <c r="L32">
+        <v>53.25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" t="s">
+        <v>30</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P32" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="s">
+        <v>33</v>
+      </c>
+      <c r="S32" t="s">
+        <v>110</v>
+      </c>
+      <c r="T32" t="s">
+        <v>142</v>
+      </c>
+      <c r="U32" t="s">
+        <v>143</v>
+      </c>
+      <c r="V32" t="s">
+        <v>144</v>
+      </c>
+      <c r="W32" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46163</v>
+      </c>
+      <c r="G33" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" t="s">
+        <v>101</v>
+      </c>
+      <c r="J33">
+        <v>48</v>
+      </c>
+      <c r="K33">
+        <v>11.77</v>
+      </c>
+      <c r="L33">
+        <v>564.96</v>
+      </c>
+      <c r="M33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" t="s">
+        <v>159</v>
+      </c>
+      <c r="O33" s="1">
+        <v>46163</v>
+      </c>
+      <c r="P33" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="s">
+        <v>33</v>
+      </c>
+      <c r="S33" t="s">
+        <v>110</v>
+      </c>
+      <c r="T33" t="s">
+        <v>161</v>
+      </c>
+      <c r="U33" t="s">
+        <v>162</v>
+      </c>
+      <c r="V33" t="s">
+        <v>163</v>
+      </c>
+      <c r="W33" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46163</v>
+      </c>
+      <c r="G34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>-62.42</v>
+      </c>
+      <c r="L34">
+        <v>-62.42</v>
+      </c>
+      <c r="M34" t="s">
+        <v>29</v>
+      </c>
+      <c r="N34" t="s">
+        <v>30</v>
+      </c>
+      <c r="O34" s="1">
+        <v>46163</v>
+      </c>
+      <c r="P34" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" t="s">
+        <v>33</v>
+      </c>
+      <c r="S34" t="s">
+        <v>110</v>
+      </c>
+      <c r="T34" t="s">
+        <v>35</v>
+      </c>
+      <c r="U34" t="s">
+        <v>36</v>
+      </c>
+      <c r="V34" t="s">
+        <v>37</v>
+      </c>
+      <c r="W34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46163</v>
+      </c>
+      <c r="G35" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35">
+        <v>72</v>
+      </c>
+      <c r="K35">
+        <v>5.78</v>
+      </c>
+      <c r="L35">
+        <v>416.16</v>
+      </c>
+      <c r="M35" t="s">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s">
+        <v>30</v>
+      </c>
+      <c r="O35" s="1">
+        <v>46163</v>
+      </c>
+      <c r="P35" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="s">
+        <v>33</v>
+      </c>
+      <c r="S35" t="s">
+        <v>110</v>
+      </c>
+      <c r="T35" t="s">
+        <v>35</v>
+      </c>
+      <c r="U35" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" t="s">
+        <v>37</v>
+      </c>
+      <c r="W35" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/activitereeldirect-2026.xlsx
+++ b/activitereeldirect-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ED8657-D29D-4878-8F4B-FEBC2D942FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F1BBF7-CB77-486A-8B37-245424B88330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52F3EE67-8AA3-4B10-A5A9-DE88DE815FD5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="228">
   <si>
     <t>N°commande</t>
   </si>
@@ -540,6 +540,186 @@
   </si>
   <si>
     <t>Mai</t>
+  </si>
+  <si>
+    <t>26416497</t>
+  </si>
+  <si>
+    <t>26617767</t>
+  </si>
+  <si>
+    <t>26331527</t>
+  </si>
+  <si>
+    <t>CODICA VI                          IVECO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86377 22                 </t>
+  </si>
+  <si>
+    <t>86377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSOR GEL CAPTEUR PLUIE PB                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0ABDM0004165             </t>
+  </si>
+  <si>
+    <t>FCI</t>
+  </si>
+  <si>
+    <t>CARPIQUET</t>
+  </si>
+  <si>
+    <t>14650</t>
+  </si>
+  <si>
+    <t>0012251-1</t>
+  </si>
+  <si>
+    <t>26414656</t>
+  </si>
+  <si>
+    <t>26615623</t>
+  </si>
+  <si>
+    <t>26415265</t>
+  </si>
+  <si>
+    <t>SOBAIE AUTOMOBILES SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87092 22                 </t>
+  </si>
+  <si>
+    <t>87092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDE SPIDER WIDER ROUL 25 M CORDE EN POLYETHYLENE           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE TEL. M. DELAPIERRE   </t>
+  </si>
+  <si>
+    <t>FBB</t>
+  </si>
+  <si>
+    <t>AVRANCHES</t>
+  </si>
+  <si>
+    <t>50300</t>
+  </si>
+  <si>
+    <t>87 RUE DU COMMANDANT BINDEL</t>
+  </si>
+  <si>
+    <t>26415606</t>
+  </si>
+  <si>
+    <t>26616846</t>
+  </si>
+  <si>
+    <t>26430259</t>
+  </si>
+  <si>
+    <t>SOBAIE AUTOMOBILES GRANVILLE SASU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85635 10                 </t>
+  </si>
+  <si>
+    <t>85635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARTOUCHE LEAK GUARD AC 4X30ML                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MR GRUNDREICH        </t>
+  </si>
+  <si>
+    <t>GRANVILLE</t>
+  </si>
+  <si>
+    <t>50400</t>
+  </si>
+  <si>
+    <t>199 RUE MARIE FOUGERAY</t>
+  </si>
+  <si>
+    <t>26414918</t>
+  </si>
+  <si>
+    <t>26615994</t>
+  </si>
+  <si>
+    <t>401134</t>
+  </si>
+  <si>
+    <t>ISIGNY ST MERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34454 22                 </t>
+  </si>
+  <si>
+    <t>34454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROTABOND 2000 BLANC 290ML                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000131381               </t>
+  </si>
+  <si>
+    <t>ISIGNY SUR MER</t>
+  </si>
+  <si>
+    <t>14230</t>
+  </si>
+  <si>
+    <t>2 RUE DU DR BOUTROIS</t>
+  </si>
+  <si>
+    <t>26615750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86680 22                 </t>
+  </si>
+  <si>
+    <t>86680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTI TAPE EVO - 50 MM X 50 M                                </t>
+  </si>
+  <si>
+    <t>26415777</t>
+  </si>
+  <si>
+    <t>26616965</t>
+  </si>
+  <si>
+    <t>26175393</t>
+  </si>
+  <si>
+    <t>568239</t>
+  </si>
+  <si>
+    <t>COMPAGNIE DES FROMAGES ET RICHESMONTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P500262823               </t>
+  </si>
+  <si>
+    <t>VIRE CEDEX</t>
+  </si>
+  <si>
+    <t>14502</t>
+  </si>
+  <si>
+    <t>1645 RUE GUY DEGRENNE</t>
+  </si>
+  <si>
+    <t>Juin</t>
   </si>
 </sst>
 </file>
@@ -921,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA07812-0C85-468D-8FD3-167ED09F5A69}">
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -3407,6 +3587,432 @@
       </c>
       <c r="W35" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
+        <v>171</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46192</v>
+      </c>
+      <c r="G36" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" t="s">
+        <v>174</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="K36">
+        <v>11.93</v>
+      </c>
+      <c r="L36">
+        <v>119.3</v>
+      </c>
+      <c r="M36" t="s">
+        <v>29</v>
+      </c>
+      <c r="N36" t="s">
+        <v>30</v>
+      </c>
+      <c r="O36" s="1">
+        <v>46191</v>
+      </c>
+      <c r="P36" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" t="s">
+        <v>176</v>
+      </c>
+      <c r="S36" t="s">
+        <v>110</v>
+      </c>
+      <c r="T36" t="s">
+        <v>177</v>
+      </c>
+      <c r="U36" t="s">
+        <v>178</v>
+      </c>
+      <c r="V36" t="s">
+        <v>179</v>
+      </c>
+      <c r="W36" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>20.358000000000001</v>
+      </c>
+      <c r="L37">
+        <v>40.716000000000001</v>
+      </c>
+      <c r="M37" t="s">
+        <v>29</v>
+      </c>
+      <c r="N37" t="s">
+        <v>30</v>
+      </c>
+      <c r="O37" s="1">
+        <v>46175</v>
+      </c>
+      <c r="P37" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="s">
+        <v>188</v>
+      </c>
+      <c r="S37" t="s">
+        <v>110</v>
+      </c>
+      <c r="T37" t="s">
+        <v>189</v>
+      </c>
+      <c r="U37" t="s">
+        <v>190</v>
+      </c>
+      <c r="V37" t="s">
+        <v>191</v>
+      </c>
+      <c r="W37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46184</v>
+      </c>
+      <c r="G38" t="s">
+        <v>196</v>
+      </c>
+      <c r="H38" t="s">
+        <v>197</v>
+      </c>
+      <c r="I38" t="s">
+        <v>198</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38">
+        <v>90.378</v>
+      </c>
+      <c r="L38">
+        <v>180.756</v>
+      </c>
+      <c r="M38" t="s">
+        <v>29</v>
+      </c>
+      <c r="N38" t="s">
+        <v>30</v>
+      </c>
+      <c r="O38" s="1">
+        <v>46183</v>
+      </c>
+      <c r="P38" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>32</v>
+      </c>
+      <c r="R38" t="s">
+        <v>188</v>
+      </c>
+      <c r="S38" t="s">
+        <v>110</v>
+      </c>
+      <c r="T38" t="s">
+        <v>200</v>
+      </c>
+      <c r="U38" t="s">
+        <v>201</v>
+      </c>
+      <c r="V38" t="s">
+        <v>202</v>
+      </c>
+      <c r="W38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G39" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" t="s">
+        <v>209</v>
+      </c>
+      <c r="J39">
+        <v>12</v>
+      </c>
+      <c r="K39">
+        <v>31.9</v>
+      </c>
+      <c r="L39">
+        <v>382.8</v>
+      </c>
+      <c r="M39" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" t="s">
+        <v>159</v>
+      </c>
+      <c r="O39" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P39" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" t="s">
+        <v>33</v>
+      </c>
+      <c r="S39" t="s">
+        <v>110</v>
+      </c>
+      <c r="T39" t="s">
+        <v>211</v>
+      </c>
+      <c r="U39" t="s">
+        <v>212</v>
+      </c>
+      <c r="V39" t="s">
+        <v>213</v>
+      </c>
+      <c r="W39" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G40" t="s">
+        <v>215</v>
+      </c>
+      <c r="H40" t="s">
+        <v>216</v>
+      </c>
+      <c r="I40" t="s">
+        <v>217</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>37.01</v>
+      </c>
+      <c r="L40">
+        <v>37.01</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" t="s">
+        <v>30</v>
+      </c>
+      <c r="O40" s="1">
+        <v>46139</v>
+      </c>
+      <c r="P40" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" t="s">
+        <v>33</v>
+      </c>
+      <c r="S40" t="s">
+        <v>110</v>
+      </c>
+      <c r="T40" t="s">
+        <v>48</v>
+      </c>
+      <c r="U40" t="s">
+        <v>49</v>
+      </c>
+      <c r="V40" t="s">
+        <v>120</v>
+      </c>
+      <c r="W40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>218</v>
+      </c>
+      <c r="B41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" t="s">
+        <v>221</v>
+      </c>
+      <c r="E41" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G41" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" t="s">
+        <v>208</v>
+      </c>
+      <c r="I41" t="s">
+        <v>209</v>
+      </c>
+      <c r="J41">
+        <v>11</v>
+      </c>
+      <c r="K41">
+        <v>19.09</v>
+      </c>
+      <c r="L41">
+        <v>209.99</v>
+      </c>
+      <c r="M41" t="s">
+        <v>29</v>
+      </c>
+      <c r="N41" t="s">
+        <v>159</v>
+      </c>
+      <c r="O41" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P41" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>32</v>
+      </c>
+      <c r="R41" t="s">
+        <v>33</v>
+      </c>
+      <c r="S41" t="s">
+        <v>110</v>
+      </c>
+      <c r="T41" t="s">
+        <v>224</v>
+      </c>
+      <c r="U41" t="s">
+        <v>225</v>
+      </c>
+      <c r="V41" t="s">
+        <v>226</v>
+      </c>
+      <c r="W41" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
